--- a/SugarAI_HLB_HAMT_60s_video_plan.xlsx
+++ b/SugarAI_HLB_HAMT_60s_video_plan.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>So we created SugarAI: one complete picture of every customer's journey.</t>
+          <t>So we bring you SugarAI: one complete picture of every customer's journey.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>So we created SugarAI: one complete picture of every customer's journey.</t>
+          <t>So we bring you SugarAI: one complete picture of every customer's journey.</t>
         </is>
       </c>
     </row>
